--- a/attached_assets/diary_1763478604977.xlsx
+++ b/attached_assets/diary_1763478604977.xlsx
@@ -530,7 +530,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Feel Panic</t>
+          <t>Feel Damp</t>
         </is>
       </c>
     </row>
